--- a/docs/Model_Execution_Workflow.xlsx
+++ b/docs/Model_Execution_Workflow.xlsx
@@ -26,6 +26,7 @@
     <t xml:space="preserve">I am using Spring Boot with MongoDB (via Spring Data MongoDB). I need two new document models added to my existing project.
 1. A `Job` document in collection `jobs` with fields:
    - jobId (String, UUID, the MongoDB _id)
+   - postingDate (Integr format yyyymmdd)
    - status (enum: PENDING, IN_PROGRESS, DONE, FAILED)
    - totalThreads (int)
    - completedThreads (int)
@@ -33,6 +34,7 @@
 2. A `JobThread` document in collection `job_threads` with fields:
    - id (String, UUID)
    - jobId (String, foreign reference to jobs)
+   - postingDate (Integr format yyyymmdd)
    - threadId (String, e.g. "partition-0")
    - partition (String)
    - status (enum: PENDING, IN_PROGRESS, DONE, FAILED)
@@ -124,8 +126,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -631,7 +636,7 @@
     <col customWidth="1" min="1" max="1" width="118.140625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="342">
+    <row r="1" ht="370.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +657,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="228">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -672,7 +677,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="213.75">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -692,7 +697,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="142.5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -712,7 +717,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="156.75">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -732,7 +737,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="270.75">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
